--- a/inspection_forms/013_inspection_maintenance_report_form--inspection_forms.xlsx
+++ b/inspection_forms/013_inspection_maintenance_report_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'warehouse_1',_'label':_'warehouse_1'}</t>
+          <t>warehouse_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Warehouse 1', 'label': 'Warehouse 1'}</t>
+          <t>Warehouse 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'warehouse_2',_'label':_'warehouse_2'}</t>
+          <t>warehouse_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Warehouse 2', 'label': 'Warehouse 2'}</t>
+          <t>Warehouse 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'warehouse_3',_'label':_'warehouse_3'}</t>
+          <t>warehouse_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Warehouse 3', 'label': 'Warehouse 3'}</t>
+          <t>Warehouse 3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'needs_inspection',_'label':_'needs_inspection'}</t>
+          <t>needs_inspection</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Needs Inspection', 'label': 'Needs Inspection'}</t>
+          <t>Needs Inspection</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'requires_repair',_'label':_'requires_repair'}</t>
+          <t>requires_repair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Requires Repair', 'label': 'Requires Repair'}</t>
+          <t>Requires Repair</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'scheduled',_'label':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Scheduled', 'label': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'rescheduled',_'label':_'rescheduled'}</t>
+          <t>rescheduled</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Rescheduled', 'label': 'Rescheduled'}</t>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'missed',_'label':_'missed'}</t>
+          <t>missed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Missed', 'label': 'Missed'}</t>
+          <t>Missed</t>
         </is>
       </c>
     </row>
